--- a/HDLBits Attempt 1/HDLBits_Tracker.xlsx
+++ b/HDLBits Attempt 1/HDLBits_Tracker.xlsx
@@ -4699,21 +4699,21 @@
       <x:c r="O7" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="e">
+      <x:c r="P7" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/151-step_one.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/151-step_one.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q7" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q7" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/151-step_one-solution.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/151-step_one-solution.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R7" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R7" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/151-step_one.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/151-step_one.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S7" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S7" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/step_one","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/step_one, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T7" s="2" t="str">
         <x:v>Drive the only output permanently high with a one-bit constant continuous assignment. No input, clock, procedural block, or stored state is required.</x:v>
@@ -4764,21 +4764,21 @@
       <x:c r="O8" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P8" s="11" t="e">
+      <x:c r="P8" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/152-zero.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/152-zero.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q8" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q8" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/152-zero.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/152-zero.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R8" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R8" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/152-zero.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/152-zero.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S8" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S8" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/zero","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/zero, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T8" s="8" t="str">
         <x:v>Drive the only output permanently low with a one-bit constant continuous assignment. This reinforces ANSI-style ports and direct combinational wiring.</x:v>
@@ -4881,21 +4881,21 @@
       <x:c r="O11" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P11" s="4" t="e">
+      <x:c r="P11" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/001-wire.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/001-wire.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q11" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/001-wire.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/001-wire.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/001-wire.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/001-wire.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S11" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S11" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/wire","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T11" s="2" t="s">
         <x:v>69</x:v>
@@ -4948,21 +4948,21 @@
       <x:c r="O12" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P12" s="11" t="e">
+      <x:c r="P12" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/002-wire4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/002-wire4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q12" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q12" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/002-wire4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/002-wire4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R12" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R12" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/002-wire4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/002-wire4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S12" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S12" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/wire4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T12" s="8" t="s">
         <x:v>73</x:v>
@@ -5015,21 +5015,21 @@
       <x:c r="O13" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P13" s="4" t="e">
+      <x:c r="P13" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/003-notgate.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/003-notgate.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q13" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q13" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/003-notgate.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/003-notgate.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R13" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/003-notgate.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/003-notgate.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S13" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S13" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/notgate","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/notgate, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T13" s="2" t="s">
         <x:v>77</x:v>
@@ -5082,21 +5082,21 @@
       <x:c r="O14" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P14" s="11" t="e">
+      <x:c r="P14" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/004-andgate.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/004-andgate.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q14" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q14" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/004-andgate.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/004-andgate.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R14" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R14" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/004-andgate.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/004-andgate.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S14" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S14" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/andgate","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/andgate, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T14" s="8" t="s">
         <x:v>81</x:v>
@@ -5149,21 +5149,21 @@
       <x:c r="O15" s="6">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P15" s="4" t="e">
+      <x:c r="P15" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/005-norgate.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/005-norgate.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q15" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q15" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/005-norgate.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/005-norgate.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R15" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R15" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/005-norgate.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/005-norgate.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S15" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S15" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/norgate","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/norgate, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T15" s="2" t="s">
         <x:v>85</x:v>
@@ -5216,21 +5216,21 @@
       <x:c r="O16" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P16" s="11" t="e">
+      <x:c r="P16" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/006-xnorgate.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/006-xnorgate.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q16" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q16" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/006-xnorgate.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/006-xnorgate.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R16" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R16" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/006-xnorgate.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/006-xnorgate.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S16" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S16" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/xnorgate","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/xnorgate, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T16" s="8" t="s">
         <x:v>89</x:v>
@@ -5283,21 +5283,21 @@
       <x:c r="O17" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P17" s="4" t="e">
+      <x:c r="P17" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/007-wire_decl.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/007-wire_decl.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q17" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q17" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/007-wire_decl.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/007-wire_decl.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R17" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R17" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/007-wire_decl.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/007-wire_decl.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S17" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S17" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/wire_decl","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/wire_decl, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T17" s="2" t="s">
         <x:v>93</x:v>
@@ -5350,21 +5350,21 @@
       <x:c r="O18" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P18" s="11" t="e">
+      <x:c r="P18" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/008-7458.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/008-7458.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q18" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q18" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/008-7458.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/008-7458.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R18" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R18" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/008-7458.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/008-7458.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S18" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S18" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/7458","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/7458, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T18" s="8" t="s">
         <x:v>97</x:v>
@@ -5442,21 +5442,21 @@
       <x:c r="O20" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P20" s="4" t="e">
+      <x:c r="P20" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/009-vector0.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/009-vector0.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q20" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q20" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/009-vector0.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/009-vector0.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R20" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R20" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/009-vector0.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/009-vector0.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S20" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S20" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector0","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector0, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T20" s="2" t="s">
         <x:v>101</x:v>
@@ -5509,21 +5509,21 @@
       <x:c r="O21" s="10">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="P21" s="11" t="e">
+      <x:c r="P21" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/010-vector1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/010-vector1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q21" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q21" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/010-vector1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/010-vector1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R21" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R21" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/010-vector1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/010-vector1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S21" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S21" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T21" s="8" t="s">
         <x:v>105</x:v>
@@ -5576,21 +5576,21 @@
       <x:c r="O22" s="6">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P22" s="4" t="e">
+      <x:c r="P22" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/011-vector2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/011-vector2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q22" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q22" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/011-vector2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/011-vector2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R22" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R22" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/011-vector2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/011-vector2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S22" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S22" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T22" s="2" t="s">
         <x:v>109</x:v>
@@ -5643,21 +5643,21 @@
       <x:c r="O23" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P23" s="11" t="e">
+      <x:c r="P23" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/012-vectorgates.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/012-vectorgates.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q23" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q23" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/012-vectorgates.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/012-vectorgates.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R23" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R23" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/012-vectorgates.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/012-vectorgates.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S23" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S23" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vectorgates","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vectorgates, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T23" s="8" t="s">
         <x:v>113</x:v>
@@ -5710,21 +5710,21 @@
       <x:c r="O24" s="6">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P24" s="4" t="e">
+      <x:c r="P24" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/013-gates4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/013-gates4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q24" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q24" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/013-gates4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/013-gates4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R24" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R24" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/013-gates4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/013-gates4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S24" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S24" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gates4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T24" s="2" t="s">
         <x:v>117</x:v>
@@ -5777,21 +5777,21 @@
       <x:c r="O25" s="10">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P25" s="11" t="e">
+      <x:c r="P25" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/014-vector3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/014-vector3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q25" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q25" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/014-vector3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/014-vector3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R25" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R25" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/014-vector3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/014-vector3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S25" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S25" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T25" s="8" t="s">
         <x:v>121</x:v>
@@ -5844,21 +5844,21 @@
       <x:c r="O26" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P26" s="4" t="e">
+      <x:c r="P26" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/015-vectorr.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/015-vectorr.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q26" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q26" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/015-vectorr.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/015-vectorr.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R26" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R26" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/015-vectorr.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/015-vectorr.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S26" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S26" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vectorr","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vectorr, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T26" s="2" t="s">
         <x:v>125</x:v>
@@ -5911,21 +5911,21 @@
       <x:c r="O27" s="10">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="P27" s="11" t="e">
+      <x:c r="P27" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/016-vector4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2001/016-vector4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q27" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q27" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/016-vector4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2001/016-vector4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R27" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R27" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/016-vector4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2001/016-vector4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S27" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S27" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T27" s="8" t="s">
         <x:v>129</x:v>
@@ -5978,21 +5978,21 @@
       <x:c r="O28" s="6">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P28" s="4" t="e">
+      <x:c r="P28" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/017-vector5.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/017-vector5.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q28" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q28" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/017-vector5.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/017-vector5.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R28" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R28" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/017-vector5.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/017-vector5.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S28" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S28" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector5","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector5, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T28" s="2" t="s">
         <x:v>133</x:v>
@@ -6070,21 +6070,21 @@
       <x:c r="O30" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P30" s="11" t="e">
+      <x:c r="P30" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/018-module.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/018-module.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q30" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q30" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/018-module.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/018-module.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R30" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R30" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/018-module.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/018-module.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S30" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S30" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T30" s="8" t="s">
         <x:v>138</x:v>
@@ -6137,21 +6137,21 @@
       <x:c r="O31" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P31" s="4" t="e">
+      <x:c r="P31" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/019-module_pos.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/019-module_pos.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q31" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q31" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/019-module_pos.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/019-module_pos.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R31" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R31" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/019-module_pos.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/019-module_pos.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S31" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S31" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_pos","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_pos, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T31" s="2" t="s">
         <x:v>142</x:v>
@@ -6204,21 +6204,21 @@
       <x:c r="O32" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P32" s="11" t="e">
+      <x:c r="P32" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/020-module_name.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/020-module_name.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q32" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q32" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/020-module_name.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/020-module_name.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R32" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R32" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/020-module_name.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/020-module_name.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S32" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S32" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_name","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_name, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T32" s="8" t="s">
         <x:v>146</x:v>
@@ -6271,21 +6271,21 @@
       <x:c r="O33" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P33" s="4" t="e">
+      <x:c r="P33" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/021-module_shift.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/021-module_shift.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q33" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q33" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/021-module_shift.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/021-module_shift.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R33" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R33" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/021-module_shift.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/021-module_shift.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S33" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S33" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_shift","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_shift, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T33" s="2" t="s">
         <x:v>150</x:v>
@@ -6338,21 +6338,21 @@
       <x:c r="O34" s="10">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P34" s="11" t="e">
+      <x:c r="P34" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/022-module_shift8.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/022-module_shift8.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q34" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q34" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/022-module_shift8.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/022-module_shift8.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R34" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R34" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/022-module_shift8.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/022-module_shift8.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S34" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S34" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_shift8","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_shift8, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T34" s="8" t="s">
         <x:v>154</x:v>
@@ -6405,21 +6405,21 @@
       <x:c r="O35" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P35" s="4" t="e">
+      <x:c r="P35" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/023-module_add.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/023-module_add.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q35" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q35" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/023-module_add.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/023-module_add.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R35" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R35" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/023-module_add.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/023-module_add.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S35" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S35" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_add","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_add, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T35" s="2" t="s">
         <x:v>158</x:v>
@@ -6472,21 +6472,21 @@
       <x:c r="O36" s="10">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P36" s="11" t="e">
+      <x:c r="P36" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/024-module_fadd.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/024-module_fadd.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q36" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q36" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/024-module_fadd.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/024-module_fadd.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R36" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R36" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/024-module_fadd.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/024-module_fadd.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S36" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S36" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_fadd","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_fadd, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T36" s="8" t="s">
         <x:v>162</x:v>
@@ -6539,21 +6539,21 @@
       <x:c r="O37" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P37" s="4" t="e">
+      <x:c r="P37" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/025-module_cseladd.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/025-module_cseladd.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q37" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q37" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/025-module_cseladd.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/025-module_cseladd.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R37" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R37" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/025-module_cseladd.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/025-module_cseladd.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S37" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S37" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_cseladd","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_cseladd, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T37" s="2" t="s">
         <x:v>166</x:v>
@@ -6606,21 +6606,21 @@
       <x:c r="O38" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P38" s="11" t="e">
+      <x:c r="P38" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/026-module_addsub.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/026-module_addsub.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q38" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q38" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/026-module_addsub.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/026-module_addsub.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R38" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R38" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/026-module_addsub.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/026-module_addsub.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S38" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S38" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/module_addsub","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/module_addsub, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T38" s="8" t="s">
         <x:v>170</x:v>
@@ -6698,21 +6698,21 @@
       <x:c r="O40" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P40" s="4" t="e">
+      <x:c r="P40" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/027-alwaysblock1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/027-alwaysblock1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q40" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q40" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/027-alwaysblock1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/027-alwaysblock1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R40" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R40" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/027-alwaysblock1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/027-alwaysblock1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S40" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S40" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/alwaysblock1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/alwaysblock1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T40" s="2" t="s">
         <x:v>175</x:v>
@@ -6765,21 +6765,21 @@
       <x:c r="O41" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P41" s="11" t="e">
+      <x:c r="P41" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/028-alwaysblock2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/028-alwaysblock2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q41" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q41" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/028-alwaysblock2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/028-alwaysblock2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R41" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R41" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/028-alwaysblock2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/028-alwaysblock2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S41" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S41" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/alwaysblock2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/alwaysblock2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T41" s="8" t="s">
         <x:v>179</x:v>
@@ -6832,21 +6832,21 @@
       <x:c r="O42" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P42" s="4" t="e">
+      <x:c r="P42" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/029-always_if.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/029-always_if.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q42" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q42" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/029-always_if.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/029-always_if.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R42" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R42" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/029-always_if.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/029-always_if.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S42" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S42" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_if","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_if, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T42" s="2" t="s">
         <x:v>183</x:v>
@@ -6899,21 +6899,21 @@
       <x:c r="O43" s="10">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="P43" s="11" t="e">
+      <x:c r="P43" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/030-always_if2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/030-always_if2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q43" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q43" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/030-always_if2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/030-always_if2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R43" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R43" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/030-always_if2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/030-always_if2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S43" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S43" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_if2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_if2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T43" s="8" t="s">
         <x:v>187</x:v>
@@ -6966,21 +6966,21 @@
       <x:c r="O44" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P44" s="4" t="e">
+      <x:c r="P44" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/031-always_case.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/031-always_case.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q44" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q44" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/031-always_case.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/031-always_case.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R44" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R44" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/031-always_case.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/031-always_case.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S44" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S44" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_case","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_case, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T44" s="2" t="s">
         <x:v>191</x:v>
@@ -7033,21 +7033,21 @@
       <x:c r="O45" s="10">
         <x:v>7.0000000000000007E-2</x:v>
       </x:c>
-      <x:c r="P45" s="11" t="e">
+      <x:c r="P45" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/032-always_case2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/032-always_case2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q45" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q45" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/032-always_case2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/032-always_case2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R45" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R45" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/032-always_case2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/032-always_case2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S45" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S45" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_case2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_case2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T45" s="8" t="s">
         <x:v>195</x:v>
@@ -7100,21 +7100,21 @@
       <x:c r="O46" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P46" s="4" t="e">
+      <x:c r="P46" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/033-always_casez.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/033-always_casez.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q46" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q46" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/033-always_casez.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/033-always_casez.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R46" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R46" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/033-always_casez.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/033-always_casez.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S46" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S46" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_casez","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_casez, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T46" s="2" t="s">
         <x:v>199</x:v>
@@ -7167,21 +7167,21 @@
       <x:c r="O47" s="10">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P47" s="11" t="e">
+      <x:c r="P47" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/034-always_nolatches.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/034-always_nolatches.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q47" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q47" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/034-always_nolatches.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/034-always_nolatches.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R47" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R47" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/034-always_nolatches.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/034-always_nolatches.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S47" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S47" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/always_nolatches","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/always_nolatches, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T47" s="8" t="s">
         <x:v>203</x:v>
@@ -7259,21 +7259,21 @@
       <x:c r="O49" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P49" s="4" t="e">
+      <x:c r="P49" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/035-conditional.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/035-conditional.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q49" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q49" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/035-conditional.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/035-conditional.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R49" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R49" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/035-conditional.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/035-conditional.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S49" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S49" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/conditional","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/conditional, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T49" s="2" t="s">
         <x:v>208</x:v>
@@ -7326,21 +7326,21 @@
       <x:c r="O50" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P50" s="11" t="e">
+      <x:c r="P50" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/036-reduction.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/036-reduction.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q50" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q50" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/036-reduction.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/036-reduction.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R50" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R50" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/036-reduction.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/036-reduction.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S50" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S50" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/reduction","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/reduction, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T50" s="8" t="s">
         <x:v>212</x:v>
@@ -7393,21 +7393,21 @@
       <x:c r="O51" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P51" s="4" t="e">
+      <x:c r="P51" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/037-gates100.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/037-gates100.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q51" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q51" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/037-gates100.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/037-gates100.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R51" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R51" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/037-gates100.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/037-gates100.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S51" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S51" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gates100","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates100, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T51" s="2" t="s">
         <x:v>216</x:v>
@@ -7460,21 +7460,21 @@
       <x:c r="O52" s="10">
         <x:v>0.38</x:v>
       </x:c>
-      <x:c r="P52" s="11" t="e">
+      <x:c r="P52" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/038-vector100r.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/038-vector100r.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q52" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q52" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/038-vector100r.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/038-vector100r.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R52" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R52" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/038-vector100r.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/038-vector100r.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S52" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S52" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/vector100r","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/vector100r, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T52" s="8" t="s">
         <x:v>220</x:v>
@@ -7527,21 +7527,21 @@
       <x:c r="O53" s="6">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="P53" s="4" t="e">
+      <x:c r="P53" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/039-popcount255.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/039-popcount255.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q53" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q53" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/039-popcount255.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/039-popcount255.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R53" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R53" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/039-popcount255.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/039-popcount255.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S53" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S53" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/popcount255","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/popcount255, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T53" s="2" t="s">
         <x:v>224</x:v>
@@ -7594,21 +7594,21 @@
       <x:c r="O54" s="10">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="P54" s="11" t="e">
+      <x:c r="P54" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/040-adder100i.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/040-adder100i.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q54" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q54" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/040-adder100i.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/040-adder100i.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R54" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R54" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/040-adder100i.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/040-adder100i.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S54" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S54" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/adder100i","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder100i, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T54" s="8" t="s">
         <x:v>228</x:v>
@@ -7661,21 +7661,21 @@
       <x:c r="O55" s="6">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P55" s="4" t="e">
+      <x:c r="P55" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/041-bcdadd100.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/041-bcdadd100.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q55" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q55" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/041-bcdadd100.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/041-bcdadd100.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R55" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R55" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/041-bcdadd100.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/041-bcdadd100.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S55" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S55" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bcdadd100","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bcdadd100, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T55" s="2" t="s">
         <x:v>232</x:v>
@@ -7778,21 +7778,21 @@
       <x:c r="O58" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P58" s="11" t="e">
+      <x:c r="P58" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/042-exams__m2014_q4h.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/042-exams__m2014_q4h.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q58" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q58" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/042-exams__m2014_q4h.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/042-exams__m2014_q4h.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R58" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R58" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/042-exams__m2014_q4h.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/042-exams__m2014_q4h.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S58" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S58" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4h","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4h, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T58" s="8" t="s">
         <x:v>238</x:v>
@@ -7845,21 +7845,21 @@
       <x:c r="O59" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P59" s="4" t="e">
+      <x:c r="P59" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/043-exams__m2014_q4i.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/043-exams__m2014_q4i.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q59" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q59" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/043-exams__m2014_q4i.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/043-exams__m2014_q4i.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R59" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R59" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/043-exams__m2014_q4i.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/043-exams__m2014_q4i.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S59" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S59" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4i","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4i, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T59" s="2" t="s">
         <x:v>242</x:v>
@@ -7912,21 +7912,21 @@
       <x:c r="O60" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P60" s="11" t="e">
+      <x:c r="P60" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/044-exams__m2014_q4e.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/044-exams__m2014_q4e.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q60" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q60" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/044-exams__m2014_q4e.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/044-exams__m2014_q4e.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R60" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R60" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/044-exams__m2014_q4e.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/044-exams__m2014_q4e.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S60" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S60" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4e","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4e, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T60" s="8" t="s">
         <x:v>246</x:v>
@@ -7979,21 +7979,21 @@
       <x:c r="O61" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P61" s="4" t="e">
+      <x:c r="P61" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/045-exams__m2014_q4f.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/045-exams__m2014_q4f.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q61" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q61" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/045-exams__m2014_q4f.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/045-exams__m2014_q4f.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R61" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R61" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/045-exams__m2014_q4f.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/045-exams__m2014_q4f.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S61" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S61" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4f","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4f, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T61" s="2" t="s">
         <x:v>250</x:v>
@@ -8046,21 +8046,21 @@
       <x:c r="O62" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P62" s="11" t="e">
+      <x:c r="P62" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/046-exams__m2014_q4g.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/046-exams__m2014_q4g.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q62" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q62" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/046-exams__m2014_q4g.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/046-exams__m2014_q4g.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R62" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R62" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/046-exams__m2014_q4g.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/046-exams__m2014_q4g.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S62" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S62" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4g","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4g, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T62" s="8" t="s">
         <x:v>254</x:v>
@@ -8113,21 +8113,21 @@
       <x:c r="O63" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P63" s="4" t="e">
+      <x:c r="P63" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/047-gates.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/047-gates.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q63" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q63" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/047-gates.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/047-gates.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R63" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R63" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/047-gates.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/047-gates.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S63" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S63" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gates","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gates, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T63" s="2" t="s">
         <x:v>258</x:v>
@@ -8180,21 +8180,21 @@
       <x:c r="O64" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P64" s="11" t="e">
+      <x:c r="P64" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/048-7420.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/048-7420.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q64" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q64" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/048-7420.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/048-7420.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R64" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R64" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/048-7420.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/048-7420.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S64" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S64" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/7420","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/7420, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T64" s="8" t="s">
         <x:v>262</x:v>
@@ -8247,21 +8247,21 @@
       <x:c r="O65" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P65" s="4" t="e">
+      <x:c r="P65" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/049-truthtable1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/049-truthtable1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q65" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q65" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/049-truthtable1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/049-truthtable1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R65" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R65" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/049-truthtable1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/049-truthtable1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S65" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S65" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/truthtable1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/truthtable1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T65" s="2" t="s">
         <x:v>266</x:v>
@@ -8314,21 +8314,21 @@
       <x:c r="O66" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P66" s="11" t="e">
+      <x:c r="P66" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/050-mt2015_eq2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/050-mt2015_eq2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q66" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q66" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/050-mt2015_eq2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/050-mt2015_eq2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R66" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R66" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/050-mt2015_eq2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/050-mt2015_eq2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S66" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S66" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_eq2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_eq2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T66" s="8" t="s">
         <x:v>270</x:v>
@@ -8381,21 +8381,21 @@
       <x:c r="O67" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P67" s="4" t="e">
+      <x:c r="P67" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/051-mt2015_q4a.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/051-mt2015_q4a.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q67" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q67" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/051-mt2015_q4a.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/051-mt2015_q4a.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R67" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R67" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/051-mt2015_q4a.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/051-mt2015_q4a.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S67" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S67" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_q4a","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4a, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T67" s="2" t="s">
         <x:v>274</x:v>
@@ -8448,21 +8448,21 @@
       <x:c r="O68" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P68" s="11" t="e">
+      <x:c r="P68" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/052-mt2015_q4b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/052-mt2015_q4b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q68" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q68" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/052-mt2015_q4b.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/052-mt2015_q4b.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R68" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R68" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/052-mt2015_q4b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/052-mt2015_q4b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S68" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S68" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_q4b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T68" s="8" t="s">
         <x:v>278</x:v>
@@ -8515,21 +8515,21 @@
       <x:c r="O69" s="6">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P69" s="4" t="e">
+      <x:c r="P69" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/053-mt2015_q4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/053-mt2015_q4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q69" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q69" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/053-mt2015_q4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/053-mt2015_q4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R69" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R69" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/053-mt2015_q4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/053-mt2015_q4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S69" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S69" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_q4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_q4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T69" s="2" t="s">
         <x:v>282</x:v>
@@ -8582,21 +8582,21 @@
       <x:c r="O70" s="10">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P70" s="11" t="e">
+      <x:c r="P70" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/054-ringer.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/054-ringer.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q70" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q70" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/054-ringer.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/054-ringer.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R70" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R70" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/054-ringer.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/054-ringer.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S70" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S70" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/ringer","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/ringer, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T70" s="8" t="s">
         <x:v>286</x:v>
@@ -8649,21 +8649,21 @@
       <x:c r="O71" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P71" s="4" t="e">
+      <x:c r="P71" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/055-thermostat.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/055-thermostat.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q71" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q71" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/055-thermostat.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/055-thermostat.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R71" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R71" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/055-thermostat.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/055-thermostat.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S71" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S71" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/thermostat","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/thermostat, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T71" s="2" t="s">
         <x:v>290</x:v>
@@ -8716,21 +8716,21 @@
       <x:c r="O72" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P72" s="11" t="e">
+      <x:c r="P72" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/056-popcount3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/056-popcount3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q72" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q72" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/056-popcount3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/056-popcount3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R72" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R72" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/056-popcount3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/056-popcount3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S72" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S72" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/popcount3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/popcount3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T72" s="8" t="s">
         <x:v>294</x:v>
@@ -8783,21 +8783,21 @@
       <x:c r="O73" s="6">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P73" s="4" t="e">
+      <x:c r="P73" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/057-gatesv.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/057-gatesv.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q73" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q73" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/057-gatesv.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/057-gatesv.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R73" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R73" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/057-gatesv.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/057-gatesv.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S73" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S73" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gatesv","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gatesv, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T73" s="2" t="s">
         <x:v>298</x:v>
@@ -8850,21 +8850,21 @@
       <x:c r="O74" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P74" s="11" t="e">
+      <x:c r="P74" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/058-gatesv100.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/058-gatesv100.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q74" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q74" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/058-gatesv100.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/058-gatesv100.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R74" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R74" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/058-gatesv100.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/058-gatesv100.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S74" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S74" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/gatesv100","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/gatesv100, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T74" s="8" t="s">
         <x:v>302</x:v>
@@ -8942,21 +8942,21 @@
       <x:c r="O76" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P76" s="4" t="e">
+      <x:c r="P76" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/059-mux2to1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/059-mux2to1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q76" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q76" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/059-mux2to1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/059-mux2to1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R76" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R76" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/059-mux2to1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/059-mux2to1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S76" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S76" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux2to1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux2to1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T76" s="2" t="s">
         <x:v>307</x:v>
@@ -9009,21 +9009,21 @@
       <x:c r="O77" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P77" s="11" t="e">
+      <x:c r="P77" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/060-mux2to1v.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/060-mux2to1v.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q77" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q77" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/060-mux2to1v.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/060-mux2to1v.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R77" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R77" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/060-mux2to1v.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/060-mux2to1v.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S77" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S77" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux2to1v","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux2to1v, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T77" s="8" t="s">
         <x:v>311</x:v>
@@ -9076,21 +9076,21 @@
       <x:c r="O78" s="6">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="P78" s="4" t="e">
+      <x:c r="P78" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/061-mux9to1v.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/061-mux9to1v.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q78" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q78" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/061-mux9to1v.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/061-mux9to1v.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R78" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R78" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/061-mux9to1v.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/061-mux9to1v.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S78" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S78" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux9to1v","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux9to1v, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T78" s="2" t="s">
         <x:v>315</x:v>
@@ -9143,21 +9143,21 @@
       <x:c r="O79" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P79" s="11" t="e">
+      <x:c r="P79" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/062-mux256to1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/062-mux256to1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q79" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q79" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/062-mux256to1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/062-mux256to1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R79" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R79" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/062-mux256to1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/062-mux256to1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S79" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S79" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux256to1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux256to1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T79" s="8" t="s">
         <x:v>319</x:v>
@@ -9210,21 +9210,21 @@
       <x:c r="O80" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P80" s="4" t="e">
+      <x:c r="P80" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/063-mux256to1v.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/063-mux256to1v.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q80" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q80" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/063-mux256to1v.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/063-mux256to1v.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R80" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R80" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/063-mux256to1v.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/063-mux256to1v.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S80" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S80" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mux256to1v","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mux256to1v, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T80" s="2" t="s">
         <x:v>323</x:v>
@@ -9302,21 +9302,21 @@
       <x:c r="O82" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P82" s="11" t="e">
+      <x:c r="P82" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/064-hadd.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/064-hadd.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q82" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q82" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/064-hadd.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/064-hadd.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R82" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R82" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/064-hadd.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/064-hadd.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S82" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S82" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/hadd","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/hadd, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T82" s="8" t="s">
         <x:v>328</x:v>
@@ -9369,21 +9369,21 @@
       <x:c r="O83" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P83" s="4" t="e">
+      <x:c r="P83" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/065-fadd.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2002/065-fadd.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q83" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q83" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/065-fadd.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2002/065-fadd.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R83" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R83" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/065-fadd.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2002/065-fadd.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S83" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S83" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fadd","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fadd, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T83" s="2" t="s">
         <x:v>332</x:v>
@@ -9436,21 +9436,21 @@
       <x:c r="O84" s="10">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P84" s="11" t="e">
+      <x:c r="P84" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/066-adder3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/066-adder3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q84" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q84" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/066-adder3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/066-adder3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R84" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R84" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/066-adder3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/066-adder3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S84" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S84" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/adder3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T84" s="8" t="s">
         <x:v>336</x:v>
@@ -9503,21 +9503,21 @@
       <x:c r="O85" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P85" s="4" t="e">
+      <x:c r="P85" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/067-exams__m2014_q4j.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/067-exams__m2014_q4j.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q85" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q85" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/067-exams__m2014_q4j.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/067-exams__m2014_q4j.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R85" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R85" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/067-exams__m2014_q4j.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/067-exams__m2014_q4j.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S85" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S85" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4j","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4j, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T85" s="2" t="s">
         <x:v>340</x:v>
@@ -9570,21 +9570,21 @@
       <x:c r="O86" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P86" s="11" t="e">
+      <x:c r="P86" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/068-exams__ece241_2014_q1c.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/068-exams__ece241_2014_q1c.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q86" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q86" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/068-exams__ece241_2014_q1c.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/068-exams__ece241_2014_q1c.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R86" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R86" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/068-exams__ece241_2014_q1c.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/068-exams__ece241_2014_q1c.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S86" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S86" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q1c","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q1c, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T86" s="8" t="s">
         <x:v>344</x:v>
@@ -9637,21 +9637,21 @@
       <x:c r="O87" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P87" s="4" t="e">
+      <x:c r="P87" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/069-adder100.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/069-adder100.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q87" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q87" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/069-adder100.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/069-adder100.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R87" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R87" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/069-adder100.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/069-adder100.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S87" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S87" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/adder100","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/adder100, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T87" s="2" t="s">
         <x:v>348</x:v>
@@ -9704,21 +9704,21 @@
       <x:c r="O88" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P88" s="11" t="e">
+      <x:c r="P88" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/070-bcdadd4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/070-bcdadd4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q88" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q88" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/070-bcdadd4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/070-bcdadd4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R88" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R88" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/070-bcdadd4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/070-bcdadd4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S88" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S88" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bcdadd4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bcdadd4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T88" s="8" t="s">
         <x:v>352</x:v>
@@ -9796,21 +9796,21 @@
       <x:c r="O90" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P90" s="4" t="e">
+      <x:c r="P90" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/071-kmap1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/071-kmap1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q90" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q90" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/071-kmap1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/071-kmap1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R90" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R90" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/071-kmap1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/071-kmap1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S90" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S90" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T90" s="2" t="s">
         <x:v>357</x:v>
@@ -9863,21 +9863,21 @@
       <x:c r="O91" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P91" s="11" t="e">
+      <x:c r="P91" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/072-kmap2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/072-kmap2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q91" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q91" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/072-kmap2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/072-kmap2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R91" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R91" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/072-kmap2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/072-kmap2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S91" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S91" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T91" s="8" t="s">
         <x:v>361</x:v>
@@ -9930,21 +9930,21 @@
       <x:c r="O92" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P92" s="4" t="e">
+      <x:c r="P92" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/073-kmap3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/073-kmap3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q92" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q92" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/073-kmap3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/073-kmap3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R92" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R92" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/073-kmap3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/073-kmap3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S92" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S92" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T92" s="2" t="s">
         <x:v>364</x:v>
@@ -9997,21 +9997,21 @@
       <x:c r="O93" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P93" s="11" t="e">
+      <x:c r="P93" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/074-kmap4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/074-kmap4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q93" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q93" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/074-kmap4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/074-kmap4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R93" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R93" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/074-kmap4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/074-kmap4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S93" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S93" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/kmap4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/kmap4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T93" s="8" t="s">
         <x:v>367</x:v>
@@ -10064,21 +10064,21 @@
       <x:c r="O94" s="6">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P94" s="4" t="e">
+      <x:c r="P94" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/075-exams__ece241_2013_q2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/075-exams__ece241_2013_q2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q94" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q94" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/075-exams__ece241_2013_q2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/075-exams__ece241_2013_q2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R94" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R94" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/075-exams__ece241_2013_q2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/075-exams__ece241_2013_q2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S94" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S94" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T94" s="2" t="s">
         <x:v>371</x:v>
@@ -10131,21 +10131,21 @@
       <x:c r="O95" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P95" s="11" t="e">
+      <x:c r="P95" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/076-exams__m2014_q3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/076-exams__m2014_q3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q95" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q95" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/076-exams__m2014_q3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/076-exams__m2014_q3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R95" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R95" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/076-exams__m2014_q3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/076-exams__m2014_q3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S95" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S95" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T95" s="8" t="s">
         <x:v>375</x:v>
@@ -10198,21 +10198,21 @@
       <x:c r="O96" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P96" s="4" t="e">
+      <x:c r="P96" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/077-exams__2012_q1g.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/077-exams__2012_q1g.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q96" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q96" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/077-exams__2012_q1g.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/077-exams__2012_q1g.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R96" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R96" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/077-exams__2012_q1g.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/077-exams__2012_q1g.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S96" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S96" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2012_q1g","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q1g, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T96" s="2" t="s">
         <x:v>378</x:v>
@@ -10265,21 +10265,21 @@
       <x:c r="O97" s="10">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P97" s="11" t="e">
+      <x:c r="P97" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/078-exams__ece241_2014_q3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/078-exams__ece241_2014_q3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q97" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q97" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/078-exams__ece241_2014_q3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/078-exams__ece241_2014_q3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R97" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R97" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/078-exams__ece241_2014_q3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/078-exams__ece241_2014_q3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S97" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S97" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T97" s="8" t="s">
         <x:v>382</x:v>
@@ -10357,21 +10357,21 @@
       <x:c r="O99" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P99" s="4" t="e">
+      <x:c r="P99" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/079-dff.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/079-dff.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q99" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q99" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/079-dff.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/079-dff.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R99" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R99" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/079-dff.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/079-dff.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S99" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S99" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T99" s="2" t="s">
         <x:v>387</x:v>
@@ -10424,21 +10424,21 @@
       <x:c r="O100" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P100" s="11" t="e">
+      <x:c r="P100" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/080-dff8.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/080-dff8.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q100" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q100" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/080-dff8.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/080-dff8.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R100" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R100" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/080-dff8.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/080-dff8.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S100" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S100" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T100" s="8" t="s">
         <x:v>391</x:v>
@@ -10491,21 +10491,21 @@
       <x:c r="O101" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P101" s="4" t="e">
+      <x:c r="P101" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/081-dff8r.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/081-dff8r.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q101" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q101" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/081-dff8r.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/081-dff8r.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R101" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R101" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/081-dff8r.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/081-dff8r.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S101" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S101" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8r","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8r, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T101" s="2" t="s">
         <x:v>395</x:v>
@@ -10558,21 +10558,21 @@
       <x:c r="O102" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P102" s="11" t="e">
+      <x:c r="P102" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/082-dff8p.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/082-dff8p.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q102" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q102" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/082-dff8p.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/082-dff8p.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R102" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R102" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/082-dff8p.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/082-dff8p.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S102" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S102" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8p","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8p, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T102" s="8" t="s">
         <x:v>399</x:v>
@@ -10625,21 +10625,21 @@
       <x:c r="O103" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P103" s="4" t="e">
+      <x:c r="P103" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/083-dff8ar.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/083-dff8ar.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q103" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q103" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/083-dff8ar.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/083-dff8ar.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R103" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R103" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/083-dff8ar.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/083-dff8ar.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S103" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S103" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff8ar","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff8ar, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T103" s="2" t="s">
         <x:v>403</x:v>
@@ -10692,21 +10692,21 @@
       <x:c r="O104" s="10">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="P104" s="11" t="e">
+      <x:c r="P104" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/084-dff16e.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/084-dff16e.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q104" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q104" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/084-dff16e.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/084-dff16e.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R104" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R104" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/084-dff16e.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/084-dff16e.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S104" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S104" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dff16e","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dff16e, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T104" s="8" t="s">
         <x:v>407</x:v>
@@ -10759,21 +10759,21 @@
       <x:c r="O105" s="6">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P105" s="4" t="e">
+      <x:c r="P105" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/085-exams__m2014_q4a.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/085-exams__m2014_q4a.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q105" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q105" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/085-exams__m2014_q4a.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/085-exams__m2014_q4a.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R105" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R105" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/085-exams__m2014_q4a.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/085-exams__m2014_q4a.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S105" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S105" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4a","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4a, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T105" s="2" t="s">
         <x:v>411</x:v>
@@ -10826,21 +10826,21 @@
       <x:c r="O106" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P106" s="11" t="e">
+      <x:c r="P106" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/086-exams__m2014_q4b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/086-exams__m2014_q4b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q106" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q106" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/086-exams__m2014_q4b.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/086-exams__m2014_q4b.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R106" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R106" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/086-exams__m2014_q4b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/086-exams__m2014_q4b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S106" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S106" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T106" s="8" t="s">
         <x:v>415</x:v>
@@ -10893,21 +10893,21 @@
       <x:c r="O107" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P107" s="4" t="e">
+      <x:c r="P107" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/087-exams__m2014_q4c.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/087-exams__m2014_q4c.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q107" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q107" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/087-exams__m2014_q4c.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/087-exams__m2014_q4c.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R107" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R107" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/087-exams__m2014_q4c.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/087-exams__m2014_q4c.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S107" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S107" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4c","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4c, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T107" s="2" t="s">
         <x:v>418</x:v>
@@ -10960,21 +10960,21 @@
       <x:c r="O108" s="10">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P108" s="11" t="e">
+      <x:c r="P108" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/088-exams__m2014_q4d.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2003/088-exams__m2014_q4d.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q108" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q108" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/088-exams__m2014_q4d.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2003/088-exams__m2014_q4d.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R108" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R108" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/088-exams__m2014_q4d.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2003/088-exams__m2014_q4d.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S108" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S108" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4d","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4d, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T108" s="8" t="s">
         <x:v>422</x:v>
@@ -11027,21 +11027,21 @@
       <x:c r="O109" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P109" s="4" t="e">
+      <x:c r="P109" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/089-mt2015_muxdff.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/089-mt2015_muxdff.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q109" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q109" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/089-mt2015_muxdff.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/089-mt2015_muxdff.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R109" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R109" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/089-mt2015_muxdff.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/089-mt2015_muxdff.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S109" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S109" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_muxdff","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_muxdff, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T109" s="2" t="s">
         <x:v>426</x:v>
@@ -11094,21 +11094,21 @@
       <x:c r="O110" s="10">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P110" s="11" t="e">
+      <x:c r="P110" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/090-exams__2014_q4a.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/090-exams__2014_q4a.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q110" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q110" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/090-exams__2014_q4a.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/090-exams__2014_q4a.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R110" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R110" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/090-exams__2014_q4a.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/090-exams__2014_q4a.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S110" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S110" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q4a","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q4a, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T110" s="8" t="s">
         <x:v>429</x:v>
@@ -11161,21 +11161,21 @@
       <x:c r="O111" s="6">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P111" s="4" t="e">
+      <x:c r="P111" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/091-exams__ece241_2014_q4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/091-exams__ece241_2014_q4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q111" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q111" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/091-exams__ece241_2014_q4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/091-exams__ece241_2014_q4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R111" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R111" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/091-exams__ece241_2014_q4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/091-exams__ece241_2014_q4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S111" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S111" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T111" s="2" t="s">
         <x:v>433</x:v>
@@ -11228,21 +11228,21 @@
       <x:c r="O112" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P112" s="11" t="e">
+      <x:c r="P112" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/092-exams__ece241_2013_q7.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/092-exams__ece241_2013_q7.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q112" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q112" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/092-exams__ece241_2013_q7.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/092-exams__ece241_2013_q7.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R112" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R112" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/092-exams__ece241_2013_q7.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/092-exams__ece241_2013_q7.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S112" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S112" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q7","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q7, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T112" s="8" t="s">
         <x:v>437</x:v>
@@ -11295,21 +11295,21 @@
       <x:c r="O113" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P113" s="4" t="e">
+      <x:c r="P113" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/093-edgedetect.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/093-edgedetect.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q113" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q113" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/093-edgedetect.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/093-edgedetect.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R113" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R113" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/093-edgedetect.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/093-edgedetect.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S113" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S113" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/edgedetect","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgedetect, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T113" s="2" t="s">
         <x:v>441</x:v>
@@ -11362,21 +11362,21 @@
       <x:c r="O114" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P114" s="11" t="e">
+      <x:c r="P114" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/094-edgedetect2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/094-edgedetect2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q114" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q114" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/094-edgedetect2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/094-edgedetect2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R114" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R114" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/094-edgedetect2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/094-edgedetect2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S114" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S114" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/edgedetect2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgedetect2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T114" s="8" t="s">
         <x:v>445</x:v>
@@ -11429,21 +11429,21 @@
       <x:c r="O115" s="6">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P115" s="4" t="e">
+      <x:c r="P115" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/095-edgecapture.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/095-edgecapture.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q115" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q115" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/095-edgecapture.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/095-edgecapture.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R115" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R115" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/095-edgecapture.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/095-edgecapture.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S115" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S115" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/edgecapture","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/edgecapture, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T115" s="2" t="s">
         <x:v>449</x:v>
@@ -11496,21 +11496,21 @@
       <x:c r="O116" s="10">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P116" s="11" t="e">
+      <x:c r="P116" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/096-dualedge.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/096-dualedge.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q116" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q116" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/096-dualedge.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/096-dualedge.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R116" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R116" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/096-dualedge.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/096-dualedge.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S116" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S116" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/dualedge","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/dualedge, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T116" s="8" t="s">
         <x:v>453</x:v>
@@ -11588,21 +11588,21 @@
       <x:c r="O118" s="6">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P118" s="4" t="e">
+      <x:c r="P118" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/097-count15.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/097-count15.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q118" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q118" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/097-count15.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/097-count15.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R118" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R118" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/097-count15.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/097-count15.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S118" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S118" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count15","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count15, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T118" s="2" t="s">
         <x:v>458</x:v>
@@ -11655,21 +11655,21 @@
       <x:c r="O119" s="10">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P119" s="11" t="e">
+      <x:c r="P119" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/098-count10.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/098-count10.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q119" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q119" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/098-count10.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/098-count10.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R119" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R119" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/098-count10.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/098-count10.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S119" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S119" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count10","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count10, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T119" s="8" t="s">
         <x:v>462</x:v>
@@ -11722,21 +11722,21 @@
       <x:c r="O120" s="6">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P120" s="4" t="e">
+      <x:c r="P120" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/099-count1to10.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/099-count1to10.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q120" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q120" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/099-count1to10.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/099-count1to10.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R120" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R120" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/099-count1to10.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/099-count1to10.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S120" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S120" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count1to10","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count1to10, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T120" s="2" t="s">
         <x:v>466</x:v>
@@ -11789,21 +11789,21 @@
       <x:c r="O121" s="10">
         <x:v>0.67</x:v>
       </x:c>
-      <x:c r="P121" s="11" t="e">
+      <x:c r="P121" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/100-countslow.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/100-countslow.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q121" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q121" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/100-countslow.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/100-countslow.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R121" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R121" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/100-countslow.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/100-countslow.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S121" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S121" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/countslow","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/countslow, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T121" s="8" t="s">
         <x:v>470</x:v>
@@ -11856,21 +11856,21 @@
       <x:c r="O122" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P122" s="49" t="e">
+      <x:c r="P122" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2008/143-exams__ece241_2014_q7a.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2008/143-exams__ece241_2014_q7a.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q122" s="49" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q122" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2008/143-exams__ece241_2014_q7a.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2008/143-exams__ece241_2014_q7a.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R122" s="49" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R122" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2008/143-exams__ece241_2014_q7a.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2008/143-exams__ece241_2014_q7a.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S122" s="49" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S122" s="49" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q7a","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q7a, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T122" s="2" t="s">
         <x:v>473</x:v>
@@ -11923,21 +11923,21 @@
       <x:c r="O123" s="10">
         <x:v>6.6666666666666666E-2</x:v>
       </x:c>
-      <x:c r="P123" s="52" t="e">
+      <x:c r="P123" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/144-exams__ece241_2014_q7b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/144-exams__ece241_2014_q7b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q123" s="52" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q123" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/144-exams__ece241_2014_q7b.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/144-exams__ece241_2014_q7b.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R123" s="52" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R123" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/144-exams__ece241_2014_q7b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/144-exams__ece241_2014_q7b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S123" s="52" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S123" s="52" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q7b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q7b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T123" s="8" t="s">
         <x:v>476</x:v>
@@ -11990,21 +11990,21 @@
       <x:c r="O124" s="6">
         <x:v>9.0909090909090912E-2</x:v>
       </x:c>
-      <x:c r="P124" s="49" t="e">
+      <x:c r="P124" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/145-countbcd.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/145-countbcd.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q124" s="49" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q124" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/145-countbcd.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/145-countbcd.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R124" s="49" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R124" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/145-countbcd.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/145-countbcd.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S124" s="49" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S124" s="49" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/countbcd","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/countbcd, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T124" s="2" t="s">
         <x:v>479</x:v>
@@ -12057,21 +12057,21 @@
       <x:c r="O125" s="10">
         <x:v>0.33333333333333331</x:v>
       </x:c>
-      <x:c r="P125" s="52" t="e">
+      <x:c r="P125" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/146-count_clock.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/146-count_clock.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q125" s="52" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q125" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/146-count_clock.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/146-count_clock.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R125" s="52" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R125" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/146-count_clock.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/146-count_clock.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S125" s="52" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S125" s="52" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/count_clock","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/count_clock, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T125" s="8" t="s">
         <x:v>482</x:v>
@@ -12149,21 +12149,21 @@
       <x:c r="O127" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P127" s="4" t="e">
+      <x:c r="P127" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/101-shift4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/101-shift4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q127" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q127" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/101-shift4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/101-shift4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R127" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R127" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/101-shift4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/101-shift4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S127" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S127" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/shift4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/shift4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T127" s="2" t="s">
         <x:v>487</x:v>
@@ -12216,21 +12216,21 @@
       <x:c r="O128" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P128" s="11" t="e">
+      <x:c r="P128" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/102-rotate100.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/102-rotate100.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q128" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q128" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/102-rotate100.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/102-rotate100.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R128" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R128" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/102-rotate100.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/102-rotate100.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S128" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S128" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/rotate100","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rotate100, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T128" s="8" t="s">
         <x:v>491</x:v>
@@ -12283,21 +12283,21 @@
       <x:c r="O129" s="6">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P129" s="4" t="e">
+      <x:c r="P129" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/103-shift18.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/103-shift18.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q129" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q129" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/103-shift18.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/103-shift18.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R129" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R129" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/103-shift18.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/103-shift18.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S129" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S129" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/shift18","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/shift18, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T129" s="2" t="s">
         <x:v>495</x:v>
@@ -12350,21 +12350,21 @@
       <x:c r="O130" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P130" s="11" t="e">
+      <x:c r="P130" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/104-lfsr5.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/104-lfsr5.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q130" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q130" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/104-lfsr5.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/104-lfsr5.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R130" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R130" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/104-lfsr5.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/104-lfsr5.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S130" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S130" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lfsr5","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lfsr5, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T130" s="8" t="s">
         <x:v>499</x:v>
@@ -12417,21 +12417,21 @@
       <x:c r="O131" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P131" s="4" t="e">
+      <x:c r="P131" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/105-mt2015_lfsr.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/105-mt2015_lfsr.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q131" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q131" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/105-mt2015_lfsr.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/105-mt2015_lfsr.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R131" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R131" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/105-mt2015_lfsr.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/105-mt2015_lfsr.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S131" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S131" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/mt2015_lfsr","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/mt2015_lfsr, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T131" s="2" t="s">
         <x:v>503</x:v>
@@ -12484,21 +12484,21 @@
       <x:c r="O132" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P132" s="11" t="e">
+      <x:c r="P132" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/106-lfsr32.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/106-lfsr32.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q132" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q132" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/106-lfsr32.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/106-lfsr32.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R132" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R132" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/106-lfsr32.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/106-lfsr32.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S132" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S132" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lfsr32","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lfsr32, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T132" s="8" t="s">
         <x:v>507</x:v>
@@ -12551,21 +12551,21 @@
       <x:c r="O133" s="6">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="P133" s="4" t="e">
+      <x:c r="P133" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/107-exams__m2014_q4k.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2004/107-exams__m2014_q4k.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q133" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q133" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/107-exams__m2014_q4k.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2004/107-exams__m2014_q4k.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R133" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R133" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/107-exams__m2014_q4k.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2004/107-exams__m2014_q4k.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S133" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S133" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q4k","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q4k, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T133" s="2" t="s">
         <x:v>511</x:v>
@@ -12618,21 +12618,21 @@
       <x:c r="O134" s="10">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P134" s="11" t="e">
+      <x:c r="P134" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/108-exams__2014_q4b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/108-exams__2014_q4b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q134" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q134" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/108-exams__2014_q4b.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/108-exams__2014_q4b.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R134" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R134" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/108-exams__2014_q4b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/108-exams__2014_q4b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S134" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S134" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q4b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q4b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T134" s="8" t="s">
         <x:v>514</x:v>
@@ -12685,21 +12685,21 @@
       <x:c r="O135" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P135" s="4" t="e">
+      <x:c r="P135" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/109-exams__ece241_2013_q12.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/109-exams__ece241_2013_q12.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q135" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q135" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/109-exams__ece241_2013_q12.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/109-exams__ece241_2013_q12.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R135" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R135" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/109-exams__ece241_2013_q12.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/109-exams__ece241_2013_q12.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S135" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S135" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q12","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q12, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T135" s="2" t="s">
         <x:v>518</x:v>
@@ -12777,21 +12777,21 @@
       <x:c r="O137" s="10" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P137" s="11" t="e">
+      <x:c r="P137" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/175-rule90.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/175-rule90.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q137" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q137" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/175-rule90-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/175-rule90-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R137" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R137" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/175-rule90.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/175-rule90.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S137" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S137" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/rule90","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rule90, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T137" s="8" t="str">
         <x:v>Rule 90 asks for a 512-cell one-dimensional cellular automaton. Each next cell is the XOR of the old left and right neighbors, with zero padding at both boundaries and synchronous load priority.</x:v>
@@ -12846,21 +12846,21 @@
       <x:c r="O138" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P138" s="4" t="e">
+      <x:c r="P138" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/176-rule110.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/176-rule110.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q138" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q138" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/176-rule110-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/176-rule110-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R138" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R138" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/176-rule110.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/176-rule110.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S138" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S138" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/rule110","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/rule110, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T138" s="2" t="str">
         <x:v>Rule 110 asks for a 512-cell automaton where each next bit comes from the old left, center, and right neighborhood according to the Rule 110 truth table, with zero-padded edges.</x:v>
@@ -12915,21 +12915,21 @@
       <x:c r="O139" s="90" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="P139" s="11" t="e">
+      <x:c r="P139" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/179-conwaylife.md","Problem note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/179-conwaylife.md, friendlyName=Problem note</x:v>
-      </x:c>
-      <x:c r="Q139" s="11" t="e">
+        <x:v>Problem note</x:v>
+      </x:c>
+      <x:c r="Q139" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/179-conwaylife-question-and-successful-submission.png","Screenshot")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/179-conwaylife-question-and-successful-submission.png, friendlyName=Screenshot</x:v>
-      </x:c>
-      <x:c r="R139" s="11" t="e">
+        <x:v>Screenshot</x:v>
+      </x:c>
+      <x:c r="R139" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/179-conwaylife.sv","Solution")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/179-conwaylife.sv, friendlyName=Solution</x:v>
-      </x:c>
-      <x:c r="S139" s="11" t="e">
+        <x:v>Solution</x:v>
+      </x:c>
+      <x:c r="S139" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/conwaylife","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/conwaylife, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T139" s="8" t="str">
         <x:v>The Game of Life state is a 16 by 16 toroidal grid packed into `q[255:0]`, with each row occupying a 16-bit slice. A cell's next value depends on the count of its eight neighbours, while the load input synchronously replaces the whole grid with `data` for initialization. The toroidal boundary condition is the important part: row 0's upper neighbour is row 15, row 15's lower neighbour is row 0, column 0's left neighbour is column 15, and column 15's right neighbour is column 0. The implementation computes those wrapped row and column indices for every cell, accumulates the eight one-bit neighbour values into an integer count, and writes the corresponding bit of `next_q`. The update rule follows the problem statement exactly. A cell becomes alive when it has exactly three neighbours. With exactly two neighbours it keeps its previous state, so the expression is `neighbours == 3 || (q[index] &amp;&amp; neighbours == 2)`. All `next_q` bits are computed combinationally from the old registered `q`, then one clock edge commits the whole generation with a nonblocking assignment. This avoids accidentally updating one cell early and letting that new value affect another cell in the same generation.</x:v>
@@ -13009,21 +13009,21 @@
       <x:c r="O141" s="6">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="P141" s="4" t="e">
+      <x:c r="P141" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/110-fsm1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/110-fsm1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q141" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q141" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/110-fsm1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/110-fsm1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R141" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R141" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/110-fsm1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/110-fsm1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S141" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S141" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T141" s="2" t="s">
         <x:v>524</x:v>
@@ -13076,21 +13076,21 @@
       <x:c r="O142" s="10">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P142" s="11" t="e">
+      <x:c r="P142" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/111-fsm1s.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/111-fsm1s.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q142" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q142" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/111-fsm1s.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/111-fsm1s.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R142" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R142" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/111-fsm1s.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/111-fsm1s.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S142" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S142" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm1s","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm1s, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T142" s="8" t="s">
         <x:v>528</x:v>
@@ -13143,21 +13143,21 @@
       <x:c r="O143" s="6">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P143" s="4" t="e">
+      <x:c r="P143" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/112-fsm2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/112-fsm2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q143" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q143" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/112-fsm2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/112-fsm2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R143" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R143" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/112-fsm2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/112-fsm2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S143" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S143" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T143" s="2" t="s">
         <x:v>532</x:v>
@@ -13210,21 +13210,21 @@
       <x:c r="O144" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P144" s="11" t="e">
+      <x:c r="P144" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/113-fsm2s.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/113-fsm2s.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q144" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q144" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/113-fsm2s.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/113-fsm2s.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R144" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R144" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/113-fsm2s.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/113-fsm2s.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S144" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S144" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm2s","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm2s, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T144" s="8" t="s">
         <x:v>536</x:v>
@@ -13277,21 +13277,21 @@
       <x:c r="O145" s="6">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P145" s="4" t="e">
+      <x:c r="P145" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/114-fsm3comb.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/114-fsm3comb.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q145" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q145" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/114-fsm3comb.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/114-fsm3comb.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R145" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R145" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/114-fsm3comb.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/114-fsm3comb.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S145" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S145" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm3comb","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3comb, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T145" s="2" t="s">
         <x:v>540</x:v>
@@ -13344,21 +13344,21 @@
       <x:c r="O146" s="10">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P146" s="11" t="e">
+      <x:c r="P146" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/115-fsm3onehot.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/115-fsm3onehot.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q146" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q146" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/115-fsm3onehot.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/115-fsm3onehot.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R146" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R146" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/115-fsm3onehot.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/115-fsm3onehot.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S146" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S146" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm3onehot","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3onehot, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T146" s="8" t="s">
         <x:v>544</x:v>
@@ -13411,21 +13411,21 @@
       <x:c r="O147" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P147" s="4" t="e">
+      <x:c r="P147" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/116-fsm3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/116-fsm3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q147" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q147" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/116-fsm3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/116-fsm3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R147" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R147" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/116-fsm3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/116-fsm3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S147" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S147" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T147" s="2" t="s">
         <x:v>548</x:v>
@@ -13478,21 +13478,21 @@
       <x:c r="O148" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P148" s="11" t="e">
+      <x:c r="P148" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/117-fsm3s.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/117-fsm3s.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q148" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q148" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/117-fsm3s.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/117-fsm3s.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R148" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R148" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/117-fsm3s.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/117-fsm3s.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S148" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S148" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm3s","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm3s, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T148" s="8" t="s">
         <x:v>552</x:v>
@@ -13545,21 +13545,21 @@
       <x:c r="O149" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P149" s="4" t="e">
+      <x:c r="P149" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/118-exams__ece241_2013_q4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/118-exams__ece241_2013_q4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q149" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q149" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/118-exams__ece241_2013_q4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/118-exams__ece241_2013_q4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R149" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R149" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/118-exams__ece241_2013_q4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/118-exams__ece241_2013_q4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S149" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S149" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T149" s="2" t="s">
         <x:v>556</x:v>
@@ -13612,21 +13612,21 @@
       <x:c r="O150" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P150" s="11" t="e">
+      <x:c r="P150" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/119-lemmings1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2005/119-lemmings1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q150" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q150" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/119-lemmings1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2005/119-lemmings1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R150" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R150" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/119-lemmings1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2005/119-lemmings1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S150" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S150" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T150" s="8" t="s">
         <x:v>560</x:v>
@@ -13679,21 +13679,21 @@
       <x:c r="O151" s="88" t="n">
         <x:v>0.047619047619047616</x:v>
       </x:c>
-      <x:c r="P151" s="4" t="e">
+      <x:c r="P151" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/159-lemmings2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/159-lemmings2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q151" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q151" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/159-lemmings2-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/159-lemmings2-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R151" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R151" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/159-lemmings2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/159-lemmings2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S151" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S151" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T151" s="2" t="str">
         <x:v>Extend the walking-direction FSM with direction-preserving falling states that ignore bumps and resume the remembered direction on landing.</x:v>
@@ -13748,21 +13748,21 @@
       <x:c r="O152" s="90" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="P152" s="11" t="e">
+      <x:c r="P152" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/160-lemmings3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2011/160-lemmings3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q152" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q152" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/160-lemmings3-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2011/160-lemmings3-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R152" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R152" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/160-lemmings3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2011/160-lemmings3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S152" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S152" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T152" s="8" t="str">
         <x:v>Add persistent digging behavior while preserving direction across the fall that begins when digging removes the ground.</x:v>
@@ -13817,21 +13817,21 @@
       <x:c r="O153" s="88" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="P153" s="4" t="e">
+      <x:c r="P153" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/161-lemmings4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/161-lemmings4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q153" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q153" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/161-lemmings4-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/161-lemmings4-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R153" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R153" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/161-lemmings4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/161-lemmings4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S153" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S153" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/lemmings4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/lemmings4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T153" s="2" t="str">
         <x:v>Add a fall-duration limit so a Lemming that falls for more than 20 cycles enters a permanent splatter state.</x:v>
@@ -13886,21 +13886,21 @@
       <x:c r="O154" s="90" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P154" s="11" t="e">
+      <x:c r="P154" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/162-fsm_onehot.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/162-fsm_onehot.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q154" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q154" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/162-fsm_onehot-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/162-fsm_onehot-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R154" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R154" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/162-fsm_onehot.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/162-fsm_onehot.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S154" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S154" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_onehot","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_onehot, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T154" s="8" t="str">
         <x:v>Derive ten one-hot next-state equations and two output equations directly from the supplied state diagram without adding state storage.</x:v>
@@ -13955,21 +13955,21 @@
       <x:c r="O155" s="88" t="n">
         <x:v>0.2727272727272727</x:v>
       </x:c>
-      <x:c r="P155" s="4" t="e">
+      <x:c r="P155" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/166-fsm_ps2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/166-fsm_ps2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q155" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q155" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/166-fsm_ps2-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/166-fsm_ps2-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R155" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R155" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/166-fsm_ps2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/166-fsm_ps2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S155" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S155" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_ps2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_ps2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T155" s="2" t="str">
         <x:v>Detect the first byte of a three-byte PS/2 packet using in[3], consume the next two bytes, and pulse done.</x:v>
@@ -14024,21 +14024,21 @@
       <x:c r="O156" s="90" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="P156" s="11" t="e">
+      <x:c r="P156" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/167-fsm_ps2data.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/167-fsm_ps2data.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q156" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q156" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/167-fsm_ps2data-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/167-fsm_ps2data-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R156" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R156" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/167-fsm_ps2data.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/167-fsm_ps2data.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S156" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S156" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_ps2data","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_ps2data, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T156" s="8" t="str">
         <x:v>Store the three PS/2 bytes in out_bytes[23:16], [15:8], and [7:0] while supporting back-to-back packets.</x:v>
@@ -14093,21 +14093,21 @@
       <x:c r="O157" s="88" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="P157" s="4" t="e">
+      <x:c r="P157" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/163-fsm_serial.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/163-fsm_serial.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q157" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q157" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/163-fsm_serial-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/163-fsm_serial-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R157" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R157" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/163-fsm_serial.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/163-fsm_serial.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S157" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S157" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_serial","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_serial, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T157" s="2" t="str">
         <x:v>Recognize a low start bit, eight data bits, and a high stop bit; pulse done and recover correctly after a malformed stop bit.</x:v>
@@ -14162,21 +14162,21 @@
       <x:c r="O158" s="90" t="n">
         <x:v>0.09090909090909091</x:v>
       </x:c>
-      <x:c r="P158" s="11" t="e">
+      <x:c r="P158" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/164-fsm_serialdata.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2012/164-fsm_serialdata.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q158" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q158" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/164-fsm_serialdata-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2012/164-fsm_serialdata-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R158" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R158" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/164-fsm_serialdata.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2012/164-fsm_serialdata.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S158" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S158" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_serialdata","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_serialdata, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T158" s="8" t="str">
         <x:v>Add an LSB-first byte datapath to the serial-frame FSM and present the reconstructed byte when done is asserted.</x:v>
@@ -14231,21 +14231,21 @@
       <x:c r="O159" s="88" t="n">
         <x:v>0.2857142857142857</x:v>
       </x:c>
-      <x:c r="P159" s="4" t="e">
+      <x:c r="P159" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/165-fsm_serialdp.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/165-fsm_serialdp.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q159" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q159" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/165-fsm_serialdp-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/165-fsm_serialdp-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R159" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R159" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/165-fsm_serialdp.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/165-fsm_serialdp.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S159" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S159" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_serialdp","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_serialdp, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T159" s="2" t="str">
         <x:v>Extend the serial receiver with odd-parity checking over eight data bits plus the parity bit, accepting only a valid stop bit and parity.</x:v>
@@ -14300,21 +14300,21 @@
       <x:c r="O160" s="90" t="n">
         <x:v>0.16666666666666666</x:v>
       </x:c>
-      <x:c r="P160" s="11" t="e">
+      <x:c r="P160" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/168-fsm_hdlc.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/168-fsm_hdlc.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q160" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q160" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/168-fsm_hdlc-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/168-fsm_hdlc-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R160" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R160" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/168-fsm_hdlc.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/168-fsm_hdlc.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S160" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S160" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/fsm_hdlc","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/fsm_hdlc, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T160" s="8" t="str">
         <x:v>Recognize HDLC discard, flag, and error patterns from consecutive-one runs and produce correctly timed output pulses.</x:v>
@@ -14369,21 +14369,21 @@
       <x:c r="O161" s="6">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="P161" s="4" t="e">
+      <x:c r="P161" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2007/142-exams__ece241_2013_q8.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2007/142-exams__ece241_2013_q8.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q161" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q161" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2007/142-exams__ece241_2013_q8.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2007/142-exams__ece241_2013_q8.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R161" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R161" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2007/142-exams__ece241_2013_q8.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2007/142-exams__ece241_2013_q8.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S161" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S161" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2013_q8","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2013_q8, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T161" s="2" t="s">
         <x:v>584</x:v>
@@ -14436,21 +14436,21 @@
       <x:c r="O162" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P162" s="11" t="e">
+      <x:c r="P162" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/169-exams__ece241_2014_q5a.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/169-exams__ece241_2014_q5a.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q162" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q162" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/169-exams__ece241_2014_q5a-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/169-exams__ece241_2014_q5a-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R162" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R162" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/169-exams__ece241_2014_q5a.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/169-exams__ece241_2014_q5a.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S162" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S162" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5a","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5a, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T162" s="8" t="str">
         <x:v>Implement a Moore serial two's-complementer that copies bits through the first 1 and inverts every later bit while processing the word least-significant bit first.</x:v>
@@ -14505,21 +14505,21 @@
       <x:c r="O163" s="6" t="n">
         <x:v>0.16666666666666666</x:v>
       </x:c>
-      <x:c r="P163" s="4" t="e">
+      <x:c r="P163" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/170-exams__ece241_2014_q5b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/170-exams__ece241_2014_q5b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q163" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q163" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/170-exams__ece241_2014_q5b-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/170-exams__ece241_2014_q5b-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R163" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R163" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/170-exams__ece241_2014_q5b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/170-exams__ece241_2014_q5b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S163" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S163" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/ece241_2014_q5b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T163" s="2" t="str">
         <x:v>Implement the Mealy version of the serial two's-complementer, where output depends on both the stored history and the current input bit.</x:v>
@@ -14574,21 +14574,21 @@
       <x:c r="O164" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P164" s="11" t="e">
+      <x:c r="P164" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/155-exams__2014_q3fsm.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/155-exams__2014_q3fsm.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q164" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q164" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/155-exams__2014_q3fsm-question-and-answer.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/155-exams__2014_q3fsm-question-and-answer.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R164" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R164" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/155-exams__2014_q3fsm.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/155-exams__2014_q3fsm.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S164" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S164" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q3fsm","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q3fsm, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T164" s="8" t="str">
         <x:v>Implement the two-state controller and its three-sample datapath so z reports whether exactly two of each three w samples are 1.</x:v>
@@ -14643,21 +14643,21 @@
       <x:c r="O165" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P165" s="4" t="e">
+      <x:c r="P165" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/156-exams__2014_q3bfsm.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/156-exams__2014_q3bfsm.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q165" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q165" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/156-exams__2014_q3bfsm-question-and-answer.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/156-exams__2014_q3bfsm-question-and-answer.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R165" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R165" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/156-exams__2014_q3bfsm.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/156-exams__2014_q3bfsm.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S165" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S165" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q3bfsm","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q3bfsm, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T165" s="2" t="str">
         <x:v>Implement the complete five-state Moore FSM directly from the supplied state-assigned transition table.</x:v>
@@ -14712,21 +14712,21 @@
       <x:c r="O166" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P166" s="11" t="e">
+      <x:c r="P166" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/157-exams__2014_q3c.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/157-exams__2014_q3c.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q166" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q166" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/157-exams__2014_q3c-question-and-answer.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/157-exams__2014_q3c-question-and-answer.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R166" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R166" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/157-exams__2014_q3c.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/157-exams__2014_q3c.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S166" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S166" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2014_q3c","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2014_q3c, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T166" s="8" t="str">
         <x:v>Derive only the next-state bit Y0 and Moore output z from the state table; no state register is required.</x:v>
@@ -14781,21 +14781,21 @@
       <x:c r="O167" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P167" s="4" t="e">
+      <x:c r="P167" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/171-exams__m2014_q6b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/171-exams__m2014_q6b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q167" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q167" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/171-exams__m2014_q6b-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/171-exams__m2014_q6b-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R167" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R167" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/171-exams__m2014_q6b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/171-exams__m2014_q6b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S167" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S167" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q6b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q6b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T167" s="2" t="str">
         <x:v>Derive one FSM next-state equation by collecting every incoming transition to the requested destination state and ORing the enabled product terms.</x:v>
@@ -14850,21 +14850,21 @@
       <x:c r="O168" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P168" s="11" t="e">
+      <x:c r="P168" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/158-exams__m2014_q6c.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2010/158-exams__m2014_q6c.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q168" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q168" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/158-exams__m2014_q6c-question-and-answer.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2010/158-exams__m2014_q6c-question-and-answer.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R168" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R168" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/158-exams__m2014_q6c.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2010/158-exams__m2014_q6c.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S168" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S168" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q6c","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q6c, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T168" s="8" t="str">
         <x:v>Write one-hot next-state equations for Y2 and Y4 from the state diagram.</x:v>
@@ -14919,21 +14919,21 @@
       <x:c r="O169" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P169" s="4" t="e">
+      <x:c r="P169" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/172-exams__m2014_q6.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/172-exams__m2014_q6.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q169" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q169" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/172-exams__m2014_q6-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/172-exams__m2014_q6-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R169" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R169" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/172-exams__m2014_q6.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/172-exams__m2014_q6.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S169" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S169" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/m2014_q6","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/m2014_q6, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T169" s="2" t="str">
         <x:v>Build the complete FSM from the given transition diagram, including synchronous reset, registered state progression, combinational next-state logic, and Moore output decode.</x:v>
@@ -14988,21 +14988,21 @@
       <x:c r="O170" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P170" s="11" t="e">
+      <x:c r="P170" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/173-exams__2012_q2fsm.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/173-exams__2012_q2fsm.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q170" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q170" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/173-exams__2012_q2fsm-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/173-exams__2012_q2fsm-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R170" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R170" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/173-exams__2012_q2fsm.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/173-exams__2012_q2fsm.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S170" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S170" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2012_q2fsm","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q2fsm, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T170" s="8" t="str">
         <x:v>Implement the state diagram as a conventional Moore FSM with reset, registered state, complete transition cases, and output decoded from the present state.</x:v>
@@ -15057,21 +15057,21 @@
       <x:c r="O171" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P171" s="4" t="e">
+      <x:c r="P171" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/174-exams__2012_q2b.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2013/174-exams__2012_q2b.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q171" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q171" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/174-exams__2012_q2b-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2013/174-exams__2012_q2b-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R171" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R171" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/174-exams__2012_q2b.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2013/174-exams__2012_q2b.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S171" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S171" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2012_q2b","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2012_q2b, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T171" s="2" t="str">
         <x:v>Write direct one-hot next-state and output equations from the same FSM, using the supplied present-state vector rather than building a state register.</x:v>
@@ -15126,21 +15126,21 @@
       <x:c r="O172" s="10" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P172" s="11" t="e">
+      <x:c r="P172" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/177-exams__2013_q2afsm.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/177-exams__2013_q2afsm.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q172" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q172" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/177-exams__2013_q2afsm-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/177-exams__2013_q2afsm-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R172" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R172" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/177-exams__2013_q2afsm.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/177-exams__2013_q2afsm.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S172" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S172" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2013_q2afsm","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2013_q2afsm, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T172" s="8" t="str">
         <x:v>Implement an arbiter FSM whose registered state selects idle or one active requester, follows the request-priority transition diagram, and decodes mutually exclusive grants.</x:v>
@@ -15195,21 +15195,21 @@
       <x:c r="O173" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P173" s="4" t="e">
+      <x:c r="P173" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/121-exams__2013_q2bfsm.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/121-exams__2013_q2bfsm.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q173" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q173" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/121-exams__2013_q2bfsm.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/121-exams__2013_q2bfsm.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R173" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R173" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/121-exams__2013_q2bfsm.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/121-exams__2013_q2bfsm.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S173" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S173" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/2013_q2bfsm","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/2013_q2bfsm, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T173" s="2" t="s">
         <x:v>596</x:v>
@@ -15287,21 +15287,21 @@
       <x:c r="O175" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P175" s="52" t="e">
+      <x:c r="P175" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/147-exams__review2015_count1k.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/147-exams__review2015_count1k.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q175" s="52" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q175" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/147-exams__review2015_count1k.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/147-exams__review2015_count1k.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R175" s="52" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R175" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/147-exams__review2015_count1k.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/147-exams__review2015_count1k.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S175" s="52" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S175" s="52" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_count1k","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_count1k, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T175" s="8" t="s">
         <x:v>600</x:v>
@@ -15354,21 +15354,21 @@
       <x:c r="O176" s="6">
         <x:v>8.3333333333333329E-2</x:v>
       </x:c>
-      <x:c r="P176" s="49" t="e">
+      <x:c r="P176" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/148-exams__review2015_shiftcount.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/148-exams__review2015_shiftcount.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q176" s="49" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q176" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/148-exams__review2015_shiftcount.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/148-exams__review2015_shiftcount.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R176" s="49" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R176" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/148-exams__review2015_shiftcount.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/148-exams__review2015_shiftcount.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S176" s="49" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S176" s="49" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_shiftcount","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_shiftcount, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T176" s="2" t="s">
         <x:v>603</x:v>
@@ -15421,21 +15421,21 @@
       <x:c r="O177" s="10">
         <x:v>8.3333333333333329E-2</x:v>
       </x:c>
-      <x:c r="P177" s="52" t="e">
+      <x:c r="P177" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/149-exams__review2015_fsmseq.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/149-exams__review2015_fsmseq.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q177" s="52" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q177" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/149-exams__review2015_fsmseq.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/149-exams__review2015_fsmseq.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R177" s="52" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R177" s="52" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/149-exams__review2015_fsmseq.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/149-exams__review2015_fsmseq.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S177" s="52" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S177" s="52" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_fsmseq","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsmseq, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T177" s="8" t="s">
         <x:v>606</x:v>
@@ -15488,21 +15488,21 @@
       <x:c r="O178" s="6">
         <x:v>0.1111111111111111</x:v>
       </x:c>
-      <x:c r="P178" s="49" t="e">
+      <x:c r="P178" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/150-exams__review2015_fsmshift.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/150-exams__review2015_fsmshift.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q178" s="49" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q178" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/150-exams__review2015_fsmshift.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/150-exams__review2015_fsmshift.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R178" s="49" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R178" s="49" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/150-exams__review2015_fsmshift.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/150-exams__review2015_fsmshift.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S178" s="49" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S178" s="49" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_fsmshift","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsmshift, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T178" s="2" t="s">
         <x:v>609</x:v>
@@ -15555,21 +15555,21 @@
       <x:c r="O179" s="10" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P179" s="11" t="e">
+      <x:c r="P179" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/153-exams__review2015_fsm.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/153-exams__review2015_fsm.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q179" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q179" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/153-exams__review2015_fsm-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/153-exams__review2015_fsm-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R179" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R179" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/153-exams__review2015_fsm.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/153-exams__review2015_fsm.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S179" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S179" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_fsm","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsm, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T179" s="8" t="str">
         <x:v>Ten-state Moore controller: search for 1101, assert shift_ena across four capture states, wait in COUNT for done_counting, then hold done in WAIT until ack. Live HDLBits verification: 2 successes, 5 incorrect attempts, 1 compile error, 8 total attempts; last success 10:20:45 PM.</x:v>
@@ -15622,21 +15622,21 @@
       <x:c r="O180" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P180" s="4" t="e">
+      <x:c r="P180" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/154-exams__review2015_fancytimer.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2009/154-exams__review2015_fancytimer.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q180" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q180" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/154-exams__review2015_fancytimer-question-and-successful-submission.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2009/154-exams__review2015_fancytimer-question-and-successful-submission.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R180" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R180" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/154-exams__review2015_fancytimer.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2009/154-exams__review2015_fancytimer.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S180" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S180" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_fancytimer","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fancytimer, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T180" s="2" t="str">
         <x:v>Complete timer with separate FSM and datapath. delay captures the four serial bits, count_remaining loads the completed value on the fourth shift edge, and a modulo-1000 counter controls each decrement. Live HDLBits verification: 2 successes from 2 attempts; last success 11:38:15 PM.</x:v>
@@ -15689,21 +15689,21 @@
       <x:c r="O181" s="90" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="P181" s="11" t="e">
+      <x:c r="P181" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/178-exams__review2015_fsmonehot.md","Problem note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2014/178-exams__review2015_fsmonehot.md, friendlyName=Problem note</x:v>
-      </x:c>
-      <x:c r="Q181" s="11" t="e">
+        <x:v>Problem note</x:v>
+      </x:c>
+      <x:c r="Q181" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/178-exams__review2015_fsmonehot-question-and-successful-submission.png","Screenshot")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2014/178-exams__review2015_fsmonehot-question-and-successful-submission.png, friendlyName=Screenshot</x:v>
-      </x:c>
-      <x:c r="R181" s="11" t="e">
+        <x:v>Screenshot</x:v>
+      </x:c>
+      <x:c r="R181" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/178-exams__review2015_fsmonehot.sv","Solution")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2014/178-exams__review2015_fsmonehot.sv, friendlyName=Solution</x:v>
-      </x:c>
-      <x:c r="S181" s="11" t="e">
+        <x:v>Solution</x:v>
+      </x:c>
+      <x:c r="S181" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/exams/review2015_fsmonehot","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/exams/review2015_fsmonehot, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T181" s="8" t="str">
         <x:v>This exercise extracts only selected one-hot equations from the complete timer controller. The supplied `state[9:0]` vector already represents the present state, so the module must not create a state register or recode the FSM. Each requested `*_next` output is the OR of every transition entering that destination state. For example, `B3_next` is high only when the current state is `B2`, because the B0-B3 shift phase advances unconditionally one state per clock. `Count_next` is high when the current state is `B3` or when the controller is already in `Count` and `done_counting` is still low. `Wait_next` is high when counting has just completed or when the controller is already waiting and `ack` has not arrived. The output equations are direct Moore decodes from the current one-hot state: `done` is `state[Wait]`, `counting` is `state[Count]`, and `shift_ena` is the OR of B0 through B3. The key review habit is destination-first derivation: list incoming arrows for each requested destination bit and translate those arrows directly into sum-of-products logic.</x:v>
@@ -15808,21 +15808,21 @@
       <x:c r="O184" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P184" s="4" t="e">
+      <x:c r="P184" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/122-bugs_mux2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/122-bugs_mux2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q184" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q184" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/122-bugs_mux2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/122-bugs_mux2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R184" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R184" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/122-bugs_mux2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/122-bugs_mux2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S184" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S184" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bugs_mux2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_mux2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T184" s="2" t="s">
         <x:v>615</x:v>
@@ -15875,21 +15875,21 @@
       <x:c r="O185" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P185" s="11" t="e">
+      <x:c r="P185" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/123-bugs_nand3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/123-bugs_nand3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q185" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q185" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/123-bugs_nand3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/123-bugs_nand3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R185" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R185" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/123-bugs_nand3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/123-bugs_nand3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S185" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S185" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bugs_nand3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_nand3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T185" s="8" t="s">
         <x:v>619</x:v>
@@ -15942,21 +15942,21 @@
       <x:c r="O186" s="6">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P186" s="4" t="e">
+      <x:c r="P186" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/124-bugs_mux4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/124-bugs_mux4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q186" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q186" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/124-bugs_mux4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/124-bugs_mux4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R186" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R186" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/124-bugs_mux4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/124-bugs_mux4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S186" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S186" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bugs_mux4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_mux4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T186" s="2" t="s">
         <x:v>622</x:v>
@@ -16009,21 +16009,21 @@
       <x:c r="O187" s="10">
         <x:v>0.17</x:v>
       </x:c>
-      <x:c r="P187" s="11" t="e">
+      <x:c r="P187" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/125-bugs_addsubz.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/125-bugs_addsubz.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q187" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q187" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/125-bugs_addsubz.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/125-bugs_addsubz.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R187" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R187" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/125-bugs_addsubz.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/125-bugs_addsubz.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S187" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S187" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bugs_addsubz","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_addsubz, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T187" s="8" t="s">
         <x:v>626</x:v>
@@ -16076,21 +16076,21 @@
       <x:c r="O188" s="6">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P188" s="4" t="e">
+      <x:c r="P188" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/126-bugs_case.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/126-bugs_case.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q188" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q188" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/126-bugs_case.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/126-bugs_case.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R188" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R188" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/126-bugs_case.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/126-bugs_case.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S188" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S188" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/bugs_case","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/bugs_case, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T188" s="2" t="s">
         <x:v>629</x:v>
@@ -16168,21 +16168,21 @@
       <x:c r="O190" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P190" s="11" t="e">
+      <x:c r="P190" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/127-sim__circuit1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/127-sim__circuit1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q190" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q190" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/127-sim__circuit1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/127-sim__circuit1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R190" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R190" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/127-sim__circuit1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/127-sim__circuit1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S190" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S190" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T190" s="8" t="s">
         <x:v>634</x:v>
@@ -16235,21 +16235,21 @@
       <x:c r="O191" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P191" s="4" t="e">
+      <x:c r="P191" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/128-sim__circuit2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/128-sim__circuit2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q191" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q191" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/128-sim__circuit2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/128-sim__circuit2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R191" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R191" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/128-sim__circuit2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/128-sim__circuit2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S191" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S191" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T191" s="2" t="s">
         <x:v>638</x:v>
@@ -16302,21 +16302,21 @@
       <x:c r="O192" s="10">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P192" s="11" t="e">
+      <x:c r="P192" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/129-sim__circuit3.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/129-sim__circuit3.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q192" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q192" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/129-sim__circuit3.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/129-sim__circuit3.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R192" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R192" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/129-sim__circuit3.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/129-sim__circuit3.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S192" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S192" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit3","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit3, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T192" s="8" t="s">
         <x:v>642</x:v>
@@ -16369,21 +16369,21 @@
       <x:c r="O193" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P193" s="4" t="e">
+      <x:c r="P193" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/130-sim__circuit4.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/130-sim__circuit4.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q193" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q193" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/130-sim__circuit4.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/130-sim__circuit4.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R193" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R193" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/130-sim__circuit4.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/130-sim__circuit4.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S193" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S193" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit4","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit4, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T193" s="2" t="s">
         <x:v>646</x:v>
@@ -16436,21 +16436,21 @@
       <x:c r="O194" s="10">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P194" s="11" t="e">
+      <x:c r="P194" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/131-sim__circuit5.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/131-sim__circuit5.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q194" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q194" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/131-sim__circuit5.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/131-sim__circuit5.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R194" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R194" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/131-sim__circuit5.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/131-sim__circuit5.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S194" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S194" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit5","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit5, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T194" s="8" t="s">
         <x:v>650</x:v>
@@ -16503,21 +16503,21 @@
       <x:c r="O195" s="6">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="P195" s="4" t="e">
+      <x:c r="P195" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/132-sim__circuit6.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/132-sim__circuit6.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q195" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q195" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/132-sim__circuit6.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/132-sim__circuit6.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R195" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R195" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/132-sim__circuit6.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/132-sim__circuit6.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S195" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S195" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit6","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit6, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T195" s="2" t="s">
         <x:v>654</x:v>
@@ -16570,21 +16570,21 @@
       <x:c r="O196" s="10">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P196" s="11" t="e">
+      <x:c r="P196" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/133-sim__circuit7.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/133-sim__circuit7.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q196" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q196" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/133-sim__circuit7.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/133-sim__circuit7.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R196" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R196" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/133-sim__circuit7.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/133-sim__circuit7.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S196" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S196" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit7","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit7, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T196" s="8" t="s">
         <x:v>658</x:v>
@@ -16637,21 +16637,21 @@
       <x:c r="O197" s="6">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="P197" s="4" t="e">
+      <x:c r="P197" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/134-sim__circuit8.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/134-sim__circuit8.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q197" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q197" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/134-sim__circuit8.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/134-sim__circuit8.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R197" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R197" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/134-sim__circuit8.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/134-sim__circuit8.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S197" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S197" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit8","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit8, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T197" s="2" t="s">
         <x:v>661</x:v>
@@ -16704,21 +16704,21 @@
       <x:c r="O198" s="10">
         <x:v>0.33</x:v>
       </x:c>
-      <x:c r="P198" s="11" t="e">
+      <x:c r="P198" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/135-sim__circuit9.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/135-sim__circuit9.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q198" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q198" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/135-sim__circuit9.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/135-sim__circuit9.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R198" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R198" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/135-sim__circuit9.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/135-sim__circuit9.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S198" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S198" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit9","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit9, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T198" s="8" t="s">
         <x:v>665</x:v>
@@ -16771,21 +16771,21 @@
       <x:c r="O199" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P199" s="4" t="e">
+      <x:c r="P199" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/136-sim__circuit10.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/136-sim__circuit10.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q199" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q199" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/136-sim__circuit10.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/136-sim__circuit10.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R199" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R199" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/136-sim__circuit10.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/136-sim__circuit10.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S199" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S199" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/sim/circuit10","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/sim/circuit10, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T199" s="2" t="s">
         <x:v>669</x:v>
@@ -16861,21 +16861,21 @@
       <x:c r="O201" s="10">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="P201" s="11" t="e">
+      <x:c r="P201" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/137-tb__clock.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/137-tb__clock.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q201" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q201" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/137-tb__clock.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/137-tb__clock.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R201" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R201" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/137-tb__clock.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/137-tb__clock.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S201" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S201" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/tb/clock","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/clock, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T201" s="8" t="s">
         <x:v>674</x:v>
@@ -16926,21 +16926,21 @@
       <x:c r="O202" s="6">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P202" s="4" t="e">
+      <x:c r="P202" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/138-tb__tb1.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/138-tb__tb1.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q202" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q202" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/138-tb__tb1.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/138-tb__tb1.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R202" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R202" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/138-tb__tb1.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/138-tb__tb1.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S202" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S202" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/tb/tb1","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/tb1, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T202" s="2" t="s">
         <x:v>678</x:v>
@@ -16991,21 +16991,21 @@
       <x:c r="O203" s="10">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P203" s="11" t="e">
+      <x:c r="P203" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/139-tb__and.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/139-tb__and.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q203" s="11" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q203" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/139-tb__and.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/139-tb__and.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R203" s="11" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R203" s="11" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/139-tb__and.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/139-tb__and.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S203" s="11" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S203" s="11" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/tb/and","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/and, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T203" s="8" t="s">
         <x:v>681</x:v>
@@ -17056,21 +17056,21 @@
       <x:c r="O204" s="6">
         <x:v>0.14000000000000001</x:v>
       </x:c>
-      <x:c r="P204" s="4" t="e">
+      <x:c r="P204" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/140-tb__tb2.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/140-tb__tb2.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q204" s="4" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q204" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/140-tb__tb2.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/140-tb__tb2.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R204" s="4" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R204" s="4" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/140-tb__tb2.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/140-tb__tb2.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S204" s="4" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S204" s="4" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/tb/tb2","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/tb2, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T204" s="2" t="s">
         <x:v>685</x:v>
@@ -17121,21 +17121,21 @@
       <x:c r="O205" s="15">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="P205" s="16" t="e">
+      <x:c r="P205" s="16" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/141-tb__tff.md","Note")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/problems/Day%2006/141-tb__tff.md, friendlyName=Note</x:v>
-      </x:c>
-      <x:c r="Q205" s="16" t="e">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="Q205" s="16" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/141-tb__tff.png","Image")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/images/Day%2006/141-tb__tff.png, friendlyName=Image</x:v>
-      </x:c>
-      <x:c r="R205" s="16" t="e">
+        <x:v>Image</x:v>
+      </x:c>
+      <x:c r="R205" s="16" t="str">
         <x:f>HYPERLINK("https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/141-tb__tff.sv","Code")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://github.com/kapiltrip/hdlBits/blob/main/study/solutions/Day%2006/141-tb__tff.sv, friendlyName=Code</x:v>
-      </x:c>
-      <x:c r="S205" s="16" t="e">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="S205" s="16" t="str">
         <x:f>HYPERLINK("https://hdlbits.01xz.net/wiki/tb/tff","HDLBits")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hdlbits.01xz.net/wiki/tb/tff, friendlyName=HDLBits</x:v>
+        <x:v>HDLBits</x:v>
       </x:c>
       <x:c r="T205" s="13" t="s">
         <x:v>689</x:v>
